--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/post FET_HRM-2031-0152/panel_11/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU 03/HRM/post FET_HRM-2031-0152/panel_11/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.6326</v>
+        <v>16.70675</v>
       </c>
       <c r="D2" t="n">
-        <v>16.52675</v>
+        <v>16.4021</v>
       </c>
       <c r="E2" t="n">
-        <v>16.93553</v>
+        <v>16.63616</v>
       </c>
       <c r="F2" t="n">
-        <v>42.43521</v>
+        <v>42.25862</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05136</v>
+        <v>0.05094</v>
       </c>
       <c r="H2" t="n">
-        <v>1.86307</v>
+        <v>1.79892</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.97395</v>
+        <v>17.20212</v>
       </c>
       <c r="D3" t="n">
-        <v>16.72633</v>
+        <v>16.62536</v>
       </c>
       <c r="E3" t="n">
-        <v>16.75935</v>
+        <v>16.74787</v>
       </c>
       <c r="F3" t="n">
-        <v>42.59317</v>
+        <v>42.32768</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05104</v>
+        <v>0.0496</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84843</v>
+        <v>1.83985</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.80167</v>
+        <v>16.80935</v>
       </c>
       <c r="D4" t="n">
-        <v>16.76003</v>
+        <v>16.65005</v>
       </c>
       <c r="E4" t="n">
-        <v>16.87004</v>
+        <v>16.74014</v>
       </c>
       <c r="F4" t="n">
-        <v>43.44196</v>
+        <v>42.67194</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0509</v>
+        <v>0.0503</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83858</v>
+        <v>1.86388</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.73556</v>
+        <v>16.62761</v>
       </c>
       <c r="D6" t="n">
-        <v>16.06573</v>
+        <v>15.92211</v>
       </c>
       <c r="E6" t="n">
-        <v>16.75541</v>
+        <v>16.5324</v>
       </c>
       <c r="F6" t="n">
-        <v>22.31339</v>
+        <v>21.72279</v>
       </c>
       <c r="G6" t="n">
-        <v>34.09182</v>
+        <v>34.71981</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.69633</v>
+        <v>17.07818</v>
       </c>
       <c r="D7" t="n">
-        <v>16.10481</v>
+        <v>16.15593</v>
       </c>
       <c r="E7" t="n">
-        <v>16.40757</v>
+        <v>16.52235</v>
       </c>
       <c r="F7" t="n">
-        <v>22.00666</v>
+        <v>21.83794</v>
       </c>
       <c r="G7" t="n">
-        <v>34.62269</v>
+        <v>34.27736</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.87079</v>
+        <v>16.84425</v>
       </c>
       <c r="D8" t="n">
-        <v>16.17502</v>
+        <v>16.22508</v>
       </c>
       <c r="E8" t="n">
-        <v>16.1611</v>
+        <v>16.39681</v>
       </c>
       <c r="F8" t="n">
-        <v>21.73623</v>
+        <v>21.97199</v>
       </c>
       <c r="G8" t="n">
-        <v>33.81549</v>
+        <v>34.55802</v>
       </c>
     </row>
   </sheetData>
